--- a/data/processed/hra_mapping_bemerkung.xlsx
+++ b/data/processed/hra_mapping_bemerkung.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C256"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,12 +526,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3x stromdüse festgeschweißt. 2x draht gewechselt und drahtseele getauscht.</t>
+          <t>3x stromdüse festgeschweißt. 2x draht gewechselt und drahtseele getauscht</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3x stromdüse festgeschweißt. 2x draht gewechselt und drahtseele getauscht.</t>
+          <t>3x stromdüse festgeschweißt. 2x draht gewechselt und drahtseele getauscht</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,12 +541,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ab 14:30 kein bediener, schweißer machen reinigung.</t>
+          <t>ab 14:30 kein bediener, schweißer machen reinigung</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ab 14:30 kein bediener, schweißer machen reinigung.</t>
+          <t>ab 14:30 kein bediener, schweißer machen reinigung</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -601,12 +601,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>abschaltsicherung, schwenkspanner war geöffnet.</t>
+          <t>abschaltsicherung, schwenkspanner war geöffnet</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>abschaltsicherung, schwenkspanner war geöffnet.</t>
+          <t>abschaltsicherung, schwenkspanner war geöffnet</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -661,12 +661,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>anlage voll, op 180 aktiv.</t>
+          <t>anlage voll, op 180 aktiv</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>anlage voll, op 180 aktiv.</t>
+          <t>anlage voll, op 180 aktiv</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,12 +676,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>auf hr gestelle warten</t>
+          <t>auf deckbleche warten</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>auf hr gestelle warten</t>
+          <t>auf deckbleche warten</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -691,42 +691,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>auftragspuffer leer, reinigung.</t>
+          <t>auf hr gestelle warten</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>auftragspuffer leer, reinigung.</t>
+          <t>auf hr gestelle warten</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>aufträge einseitig. will 2 verschiedene aufträge in einer zelle packen. robtech informiert.</t>
+          <t>auftragspuffer leer, reinigung</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>aufträge einseitig. will 2 verschiedene aufträge in einer zelle packen. robtech informiert.</t>
+          <t>auftragspuffer leer, reinigung</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ausrichrstation</t>
+          <t>aufträge einseitig. will 2 verschiedene aufträge in einer zelle packen. robtech informiert</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ausrichrstation</t>
+          <t>aufträge einseitig. will 2 verschiedene aufträge in einer zelle packen. robtech informiert</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -736,12 +736,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ausrichtastation</t>
+          <t>ausrichrstation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ausrichtastation</t>
+          <t>ausrichrstation</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -751,42 +751,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ausrichtstation</t>
+          <t>ausrichtastation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ausrichtstation</t>
+          <t>ausrichtastation</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>141</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ausrichtstation / einzelaufträge</t>
+          <t>ausrichtstation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ausrichtstation / einzelaufträge</t>
+          <t>ausrichtstation</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ausrichtstation, kl. lattentasche rechts.</t>
+          <t>ausrichtstation / einzelaufträge</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ausrichtstation, kl. lattentasche rechts.</t>
+          <t>ausrichtstation / einzelaufträge</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -796,27 +796,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ausrichtstation, kl. lattentasche.</t>
+          <t>ausrichtstation, kl. lattentasche</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ausrichtstation, kl. lattentasche.</t>
+          <t>ausrichtstation, kl. lattentasche</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ausrichstation, kl. lattentasche.</t>
+          <t>bauteil im handbetrieb gesägt</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ausrichtstation, kl. lattentasche.</t>
+          <t>bauteil im handbetrieb gesägt</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -826,42 +826,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ausrichtstation.</t>
+          <t>bauteil liegt nicht richtig drin</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ausrichtstation.</t>
+          <t>bauteil liegt nicht richtig drin</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bauteil im handbetrieb gesägt</t>
+          <t>bauteil manuell gesägt</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>bauteil im handbetrieb gesägt</t>
+          <t>bauteil manuell gesägt</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bauteil liegt nicht richtig drin</t>
+          <t>bauteilerkennung klemmt</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>bauteil liegt nicht richtig drin</t>
+          <t>bauteilerkennung klemmt</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -871,27 +871,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bauteil manuell gesägt.</t>
+          <t>betriebsversammlung</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>bauteil manuell gesägt.</t>
+          <t>betriebsversammlung</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bauteilerkennung klemmt</t>
+          <t>bleiben im leoni stehen</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>bauteilerkennung klemmt</t>
+          <t>bleiben im leoni stehen</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -901,27 +901,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bei anfahrt: hefter 3. scharnierlager, l:2514.</t>
+          <t>bleibt im leoni stehen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>bei anfahrt: hefter 3. scharnierlager, l:2514.</t>
+          <t>bleibt im leoni stehen</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>betriebsversammlung</t>
+          <t>bleibt im leoni stehen / gereinigt</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>betriebsversammlung</t>
+          <t>bleibt im leoni stehen / gereinigt</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -931,12 +931,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bleiben im leoni stehen</t>
+          <t>bleibt in brennerreinigung brenner getauscht und gerichtet position nachteachen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bleiben im leoni stehen</t>
+          <t>bleibt in brennerreinigung brenner getauscht und gerichtet position nachteachen</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -946,102 +946,102 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bleibt im leoni stehen</t>
+          <t>bleibt in brennerreinigung stecken</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bleibt im leoni stehen</t>
+          <t>bleibt in brennerreinigung stecken</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bleibt im leoni stehen / gereinigt</t>
+          <t>bleibt in der brennerreinigung stecken</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bleibt im leoni stehen / gereinigt</t>
+          <t>bleibt in der brennerreinigung stecken</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bleibt in brennerreinigung brenner getauscht und gerichtet position nachteachen</t>
+          <t>bleibt in der leoni stehen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bleibt in brennerreinigung brenner getauscht und gerichtet position nachteachen</t>
+          <t>bleibt in der leoni stehen</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bleibt in brennerreinigung stecken</t>
+          <t>bleibt in leoni stehen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bleibt in brennerreinigung stecken</t>
+          <t>bleibt in leoni stehen</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bleibt in der brennerreinigung stecken.</t>
+          <t>bleibt mit bauteil von op130.3 nach 150 stehen 2x, rob tech informiert räumen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bleibt in der brennerreinigung stecken.</t>
+          <t>bleibt mit bauteil von op130.3 nach 150 stehen 2x, rob tech informiert räumen</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bleibt in der brennerreinigung stecken</t>
+          <t>bohrer getauscht</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>bleibt in der brennerreinigung stecken.</t>
+          <t>bohrer getauscht</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bleibt in der leoni stehen</t>
+          <t>brand !!!! rob tech / schlosser informiert</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bleibt in der leoni stehen</t>
+          <t>brand !!!! rob tech / schlosser informiert</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1051,12 +1051,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bleibt in leoni stehen.</t>
+          <t>brenner getauscht / bleibt in brennerreinigung stehen rob tech informiert</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bleibt in leoni stehen.</t>
+          <t>brenner getauscht / bleibt in brennerreinigung stehen rob tech informiert</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1066,12 +1066,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bleibt mit bauteil von op130.3 nach 150 stehen 2x, rob tech informiert räumen</t>
+          <t>brenner richten</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>bleibt mit bauteil von op130.3 nach 150 stehen 2x, rob tech informiert räumen</t>
+          <t>brenner richten</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1081,42 +1081,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bohrer getauscht</t>
+          <t>brenner richten durch rob tech</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>bohrer getauscht</t>
+          <t>brenner richten durch rob tech</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>brand !!!! rob tech / schlosser informiert</t>
+          <t>brenner und schlauchpaket tauschen durch rob tech gasdurchfluss zu gering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>brand !!!! rob tech / schlosser informiert</t>
+          <t>brenner und schlauchpaket tauschen durch rob tech gasdurchfluss zu gering</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>brenner getauscht / bleibt in brennerreinigung stehen rob tech informiert</t>
+          <t>brennerreinigung defekt, rob tech informiert</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>brenner getauscht / bleibt in brennerreinigung stehen rob tech informiert</t>
+          <t>brennerreinigung defekt, rob tech informiert</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1126,42 +1126,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>brenner richten durch rob tech</t>
+          <t>crash in 2.1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>brenner richten durch rob tech</t>
+          <t>crash in 2.1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>brenner und schlauchpaket tauschen durch rob tech gasdurchfluss zu gering</t>
+          <t>crash in op 150</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>brenner und schlauchpaket tauschen durch rob tech gasdurchfluss zu gering</t>
+          <t>crash in op 150</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>brennerreinigung defekt, rob tech informiert</t>
+          <t>db 2.2 falsch gepackt soll 2900 ist 2764</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>brennerreinigung defekt, rob tech informiert</t>
+          <t>db 2.2 falsch gepackt soll 2900 ist 2764</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1171,42 +1171,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>crash in 2.1</t>
+          <t>db 2.4 falsch gepackt soll 2900 ist 2750</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>crash in 2.1</t>
+          <t>db 2.4 falsch gepackt soll 2900 ist 2750</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>crash in op 150</t>
+          <t>db fallengelassen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>crash in op 150</t>
+          <t>db fallengelassen</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>db 2.2 falsch gepackt soll 2900 ist 2764</t>
+          <t>db gestell 2.1 falsch gepackt reihenfolge passt nicht</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>db 2.2 falsch gepackt soll 2900 ist 2764</t>
+          <t>db gestell 2.1 falsch gepackt reihenfolge passt nicht</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1216,12 +1216,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>db 2.4 falsch gepackt soll 2900 ist 2750</t>
+          <t>db gestell 2.5 falsch gepackt soll 2750 ist 2900</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>db 2.4 falsch gepackt soll 2900 ist 2750</t>
+          <t>db gestell 2.5 falsch gepackt soll 2750 ist 2900</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1231,12 +1231,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>db fallengelassen</t>
+          <t>db zu wenig gepackt 2.7 l : 2814 re</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>db fallengelassen</t>
+          <t>db zu wenig gepackt 2.7 l : 2814 re</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1246,12 +1246,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>db gestell 2.1 falsch gepackt reihenfolge passt nicht</t>
+          <t>db. schief abgelegt</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>db gestell 2.1 falsch gepackt reihenfolge passt nicht</t>
+          <t>db. schief abgelegt</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1261,12 +1261,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>db gestell 2.5 falsch gepackt soll 2750 ist 2900</t>
+          <t>db.007, gepackte deckblechreihenfolge stimmt nicht mit pufferreihenfolge überein</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>db gestell 2.5 falsch gepackt soll 2750 ist 2900</t>
+          <t>db.007, gepackte deckblechreihenfolge stimmt nicht mit pufferreihenfolge überein</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1276,12 +1276,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>db zu wenig gepackt 2.7 l : 2814 re</t>
+          <t>deckblech fallen gelassen, schanierhalter schief</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>db zu wenig gepackt 2.7 l : 2814 re</t>
+          <t>deckblech fallen gelassen, schanierhalter schief</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1291,132 +1291,132 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>db. schief abgelegt</t>
+          <t>deckblech macht einen bogen, l: 2814</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>db. schief abgelegt</t>
+          <t>deckblech macht einen bogen, l: 2814</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>db.007, gepackte deckblechreihenfolge stimmt nicht mit pufferreihenfolge überein.</t>
+          <t>deckblech manuell in op 100 l eingelegt</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>db.007, gepackte deckblechreihenfolge stimmt nicht mit pufferreihenfolge überein.</t>
+          <t>deckblech manuell in op 100 l eingelegt</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>deckblech fallen gelassen</t>
+          <t>deckblech manuell in op 100 r eingelegt</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>deckblech fallen gelassen</t>
+          <t>deckblech manuell in op 100 r eingelegt</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>deckblech fallen gelassen, schanierhalter schief</t>
+          <t>deckbleche machen einen bogen, l : 2814</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>deckblech fallen gelassen, schanierhalter schief</t>
+          <t>deckbleche machen einen bogen, l : 2814</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>deckblech l: 2814.</t>
+          <t>deckbleche machen einen leichten bogen, l : 2814</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>deckblech l: 2814.</t>
+          <t>deckbleche machen einen leichten bogen, l : 2814</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>deckblech macht einen bogen, l: 2814.</t>
+          <t>deckblechgestell 2.7 falsch gepackt, kommissionierer informiert, warten auf neue deckbleche</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>deckblech macht einen bogen, l: 2814.</t>
+          <t>deckblechgestell 2.7 falsch gepackt, kommissionierer informiert, warten auf neue deckbleche</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>deckblech manuell in op 100 l eingelegt.</t>
+          <t>differenzieren</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>deckblech manuell in op 100 l eingelegt.</t>
+          <t>differenzieren</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>deckblech manuell in op 100 r eingelegt.</t>
+          <t>draht festgebrannt</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>deckblech manuell in op 100 r eingelegt.</t>
+          <t>draht festgebrannt</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>deckbleche machen einen bogen, l : 2814.</t>
+          <t>drahtfestbrand</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>deckbleche machen einen bogen, l : 2814.</t>
+          <t>drahtfestbrand</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1426,12 +1426,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>deckbleche machen einen leichten bogen, l : 2814.</t>
+          <t>drahtförderwege gereinigt</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>deckbleche machen einen leichten bogen, l : 2814.</t>
+          <t>drahtförderwege gereinigt</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1441,12 +1441,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>deckblechgestell 2.7 falsch gepackt, kommissionierer informiert, warten auf neue deckbleche.</t>
+          <t>drahtseele tauschen</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>deckblechgestell 2.7 falsch gepackt, kommissionierer informiert, warten auf neue deckbleche.</t>
+          <t>drahtseele tauschen</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1456,57 +1456,57 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>differenzieren</t>
+          <t>düsen gereinigt</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>differenzieren</t>
+          <t>düsen gereinigt</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>draht festgebrannt.</t>
+          <t>einzelaufträge</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>draht festgebrannt.</t>
+          <t>einzelaufträge</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>drahtfestbrand</t>
+          <t>erstes schanier, 1ter heftpunkt</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>drahtfestbrand</t>
+          <t>erstes schanier, 1ter heftpunkt</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>drahtseele tauschen</t>
+          <t>es wird ständig angezeigt,dass zylinder von verstärkungsprofil nicht entspannt ist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>drahtseele tauschen</t>
+          <t>es wird ständig angezeigt,dass zylinder von verstärkungsprofil nicht entspannt ist</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1516,57 +1516,57 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>düsen gereinigt.</t>
+          <t>falsches deckblech kommissioniert</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>düsen gereinigt.</t>
+          <t>falsches deckblech kommissioniert</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>einzelaufträge</t>
+          <t>fehler beim messen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>einzelaufträge</t>
+          <t>fehler beim messen</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>erstes schanier, 1ter heftpunkt</t>
+          <t>fehler beim messen. rob tech informiert</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>erstes schanier, 1ter heftpunkt</t>
+          <t>fehler beim messen. rob tech informiert</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>es wird ständig angezeigt,dass zylinder von verstärkungsprofil nicht entspannt ist.</t>
+          <t>festgebrannt und kollissionsbox ausgelöst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>es wird ständig angezeigt,dass zylinder von verstärkungsprofil nicht entspannt ist.</t>
+          <t>festgebrannt und kollissionsbox ausgelöst</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1576,12 +1576,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>falsches deckblech kommissioniert</t>
+          <t>feuer am schwenkspanner mittig rechts, rob tech informiert, wöchentlicher wartungsplan und reinigung</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>falsches deckblech kommissioniert</t>
+          <t>feuer am schwenkspanner mittig rechts, rob tech informiert, wöchentlicher wartungsplan und reinigung</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1591,57 +1591,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>fehler bei der suchfahrt aus box 1.4. rob tech informiert</t>
+          <t>fährt nicht auf position rob tech informiert</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>fehler bei der suchfahrt aus box 1.4. rob tech informiert</t>
+          <t>fährt nicht auf position rob tech informiert</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>fehler beim messen</t>
+          <t>fährt nicht auf startposition scharnierlager 3 schweißen, robtech informiert</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fehler beim messen</t>
+          <t>fährt nicht auf startposition scharnierlager 3 schweißen, robtech informiert</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>fehler beim messen. rob tech informiert</t>
+          <t>führungszapfen wieder befestigt 1.4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>fehler beim messen. rob tech informiert</t>
+          <t>führungszapfen wieder befestigt 1.4</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>fehler im programm für scharnierlagersuchfahrt bei l: 2650, robtech informiert.</t>
+          <t>für absauganlage, drahttonnen verschieben</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fehler im programm für scharnierlagersuchfahrt bei l: 2650, robtech informiert.</t>
+          <t>für absauganlage, drahttonnen verschieben</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1651,27 +1651,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>fehlersuche mit robotertechniker.</t>
+          <t>gasdurchfluss zu niedrig rob tech informiert</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>fehlersuche mit robotertechniker.</t>
+          <t>gasdurchfluss zu niedrig rob tech informiert</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>festgebrannt und kollissionsbox ausgelöst</t>
+          <t>gasdüse gereinigt</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>festgebrannt und kollissionsbox ausgelöst</t>
+          <t>gasdüse gereinigt</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1681,42 +1681,42 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>feuer am schwenkspanner mittig rechts, rob tech informiert, wöchentlicher wartungsplan und reinigung</t>
+          <t>gasdüse reinigen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>feuer am schwenkspanner mittig rechts, rob tech informiert, wöchentlicher wartungsplan und reinigung</t>
+          <t>gasdüse reinigen</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>fährt nicht auf position rob tech informiert</t>
+          <t>gestell 2.2 falsch gepackt soll 2850 ist 2900 kein li. db 036 op 70/ op 25 b li geräumt</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>fährt nicht auf position rob tech informiert</t>
+          <t>gestell 2.2 falsch gepackt soll 2850 ist 2900 kein li. db 036 op 70/ op 25 b li geräumt</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>fährt nicht auf startposition scharnierlager 3 schweißen, robtech informiert.</t>
+          <t>greifer abgerissen, rob tech informiert</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>fährt nicht auf startposition scharnierlager 3 schweißen, robtech informiert.</t>
+          <t>greifer abgerissen, rob tech informiert</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1726,12 +1726,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>führungszapfen wieder befestigt 1.4</t>
+          <t>greifer defekt, rob tech informiert</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>führungszapfen wieder befestigt 1.4</t>
+          <t>greifer defekt, rob tech informiert</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1741,27 +1741,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>für absauganlage, drahttonnen verschieben</t>
+          <t>hat bauteil falsch abgelegt op 40 r</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>für absauganlage, drahttonnen verschieben</t>
+          <t>hat bauteil falsch abgelegt op 40 r</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>gasdurchfluss zu niedrig rob tech informiert</t>
+          <t>hat bauteil falsch abgelegt op40 re</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>gasdurchfluss zu niedrig rob tech informiert</t>
+          <t>hat bauteil falsch abgelegt op40 re</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1771,12 +1771,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>gasdüse gereinigt</t>
+          <t>hat bauteil nicht aus op 180 l bekommen</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>gasdüse gereinigt</t>
+          <t>hat bauteil nicht aus op 180 l bekommen</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1786,27 +1786,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>gasdüse reinigen</t>
+          <t>hat db fallen gelassen</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>gasdüse reinigen</t>
+          <t>hat db fallen gelassen</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>gestell 2.2 falsch gepackt soll 2850 ist 2900 kein li. db 036 op 70/ op 25 b li geräumt</t>
+          <t>hat db fallengelassen</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>gestell 2.2 falsch gepackt soll 2850 ist 2900 kein li. db 036 op 70/ op 25 b li geräumt</t>
+          <t>hat db fallen gelassen</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1816,42 +1816,42 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>greifer abgerissen, rob tech informiert</t>
+          <t>hat db falsch abgelegt</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>greifer abgerissen, rob tech informiert</t>
+          <t>hat db falsch abgelegt</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>greifer defekt, rob tech informiert</t>
+          <t>hat db falsch abgelegt l 2814</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>greifer defekt, rob tech informiert</t>
+          <t>hat db falsch abgelegt l 2814</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>hat bauteil falsch abgelegt op 40 r</t>
+          <t>hat db falsch abgelegt l= 2814</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>hat bauteil falsch abgelegt op 40 r</t>
+          <t>hat db falsch abgelegt l 2814</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1861,117 +1861,117 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>hat bauteil falsch abgelegt op40 re</t>
+          <t>hat deckblech nicht aus 2.3 bekommen (abstandshalter verbogen)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>hat bauteil falsch abgelegt op40 re</t>
+          <t>hat deckblech nicht aus 2.3 bekommen (abstandshalter verbogen)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>hat bauteil nicht aus op 180 l bekommen.</t>
+          <t>hat keine schubladenzuweisung</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>hat bauteil nicht aus op 180 l bekommen.</t>
+          <t>hat keine schubladenzuweisung</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>hat db fallen gelassen</t>
+          <t>hat keine schubladenzuweisung rob tech informiert</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>hat db fallen gelassen</t>
+          <t>hat keine schubladenzuweisung rob tech informiert</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>hat db fallengelassen</t>
+          <t>hat rollprofil falsch abgelegt</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>hat db fallen gelassen</t>
+          <t>hat rollprofil falsch abgelegt</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>hat db falsch abgelegt</t>
+          <t>hydraulikleckage am knickgelenk. schlosser informiert</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>hat db falsch abgelegt</t>
+          <t>hydraulikleckage am knickgelenk. schlosser informiert</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>hat db falsch abgelegt l 2814</t>
+          <t>hydraulikleckage, schlosser informiert</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>hat db falsch abgelegt l 2814</t>
+          <t>hydraulikleckage, schlosser informiert</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>hat db falsch abgelegt l= 2814</t>
+          <t>hydrauliklackage, schlosser informiert</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>hat db falsch abgelegt l 2814</t>
+          <t>hydraulikleckage, schlosser informiert</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>hat deckblech nicht aus 2.3 bekommen (abstandshalter verbogen).</t>
+          <t>hydraulikschlauch defekt knickgelenk schlosser informiert</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>hat deckblech nicht aus 2.3 bekommen (abstandshalter verbogen).</t>
+          <t>hydraulikschlauch defekt knickgelenk schlosser informiert</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -1981,57 +1981,57 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>hat keine schubladenzuweisung</t>
+          <t>hydraulikschlauch defekt schlosser informiert</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>hat keine schubladenzuweisung</t>
+          <t>hydraulikschlauch defekt schlosser informiert</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>hat keine schubladenzuweisung rob tech informiert</t>
+          <t>hydraulikschlauch geplatzt</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>hat keine schubladenzuweisung rob tech informiert</t>
+          <t>hydraulikschlauch geplatzt</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>hat rollprofil falsch abgelegt</t>
+          <t>hydraulikschlauch gerissen, schlosser informiert</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>hat rollprofil falsch abgelegt</t>
+          <t>hydraulikschlauch gerissen, schlosser informiert</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>hydraulikleckage am knickgelenk. schlosser informiert</t>
+          <t>hydraulikschlauch kaputt. vorsp. schließt nicht. schlosser informiert</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>hydraulikleckage am knickgelenk. schlosser informiert</t>
+          <t>hydraulikschlauch kaputt. vorsp. schließt nicht. schlosser informiert</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2041,102 +2041,102 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>hydraulikleckage, schlosser informiert</t>
+          <t>hydraulikzylinder spannt nicht! rob tech informiert</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>hydraulikleckage, schlosser informiert</t>
+          <t>hydraulikzylinder spannt nicht! rob tech informiert</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hydrauliklackage, schlosser informiert</t>
+          <t>hyraulikleckage , schlosser informiert</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>hydraulikleckage, schlosser informiert</t>
+          <t>hyraulikleckage , schlosser informiert</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>hydraulikschlauch defekt knickgelenk schlosser informiert</t>
+          <t>im programm stehen geblieben</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>hydraulikschlauch defekt knickgelenk schlosser informiert</t>
+          <t>im programm stehen geblieben</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>hydraulikschlauch defekt schlosser informiert</t>
+          <t>kabel durchtrennt. kabelkanal klipps gelöst. ist an schraube hängen geblieben</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>hydraulikschlauch defekt schlosser informiert</t>
+          <t>kabel durchtrennt. kabelkanal klipps gelöst. ist an schraube hängen geblieben</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>hydraulikschlauch geplatzt.</t>
+          <t>kabel neu verlegen durch rob tech reinigung</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>hydraulikschlauch geplatzt.</t>
+          <t>kabel neu verlegen durch rob tech reinigung</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>hydraulikschlauch gerissen, schlosser informiert.</t>
+          <t>kein scharnierlager vorhanden per hand eingeschweißt</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>hydraulikschlauch gerissen, schlosser informiert.</t>
+          <t>kein scharnierlager vorhanden per hand eingeschweißt</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>hydraulikschlauch kaputt. vorsp. schließt nicht. schlosser informiert</t>
+          <t>keine deckbleche, falsche deckbleche kommissioniert soll: 2814, ist: 2750, kein richtiges vormaterial verfügbar</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>hydraulikschlauch kaputt. vorsp. schließt nicht. schlosser informiert</t>
+          <t>keine deckbleche, falsche deckbleche kommissioniert soll: 2814, ist: 2750, kein richtiges vormaterial verfügbar</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2146,12 +2146,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>hydraulikzylinder spannt nicht! rob tech informiert</t>
+          <t>keine hr gestelle</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>hydraulikzylinder spannt nicht! rob tech informiert</t>
+          <t>keine hr gestelle</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2161,12 +2161,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>hyraulikleckage , schlosser informiert</t>
+          <t>keine hr gestelle !!! reinigung</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>hyraulikleckage , schlosser informiert</t>
+          <t>keine hr gestelle !!! reinigung</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2176,27 +2176,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>im programm stehen geblieben.</t>
+          <t>keine schubladenzuweisung</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>im programm stehen geblieben.</t>
+          <t>keine schubladenzuweisung</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kabel durchtrennt. kabelkanal klipps gelöst. ist an schraube hängen geblieben.</t>
+          <t>klemmt in 1.2</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>kabel durchtrennt. kabelkanal klipps gelöst. ist an schraube hängen geblieben.</t>
+          <t>klemmt in 1.2</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2206,12 +2206,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kabel neu verlegen durch rob tech reinigung</t>
+          <t>klemmt in 1.3</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>kabel neu verlegen durch rob tech reinigung</t>
+          <t>klemmt in 1.3</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2221,42 +2221,42 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kein scharnierlager vorhanden per hand eingeschweißt</t>
+          <t>klemmt in op 150</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>kein scharnierlager vorhanden per hand eingeschweißt</t>
+          <t>klemmt in op 150</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>keine deckbleche, falsche deckbleche kommissioniert soll: 2814, ist: 2750, kein richtiges vormaterial verfügbar.</t>
+          <t>klemmt in op150</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>keine deckbleche, falsche deckbleche kommissioniert soll: 2814, ist: 2750, kein richtiges vormaterial verfügbar.</t>
+          <t>klemmt in op150</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>keine hr gestelle</t>
+          <t>knickgelenk</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>keine hr gestelle</t>
+          <t>knickgelenk</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2266,12 +2266,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>keine hr gestelle !!! reinigung</t>
+          <t>knickgelenk kabel angeschmort rob tech informiert</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>keine hr gestelle !!! reinigung</t>
+          <t>knickgelenk kabel angeschmort rob tech informiert</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2281,72 +2281,72 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>klemmt in 1.3</t>
+          <t>knickgelenk öffnet nicht</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>klemmt in 1.3</t>
+          <t>knickgelenk öffnet nicht</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>klemmt in op 150</t>
+          <t>knickgelenk öffnet nicht im automatikbetrieb</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>klemmt in op 150</t>
+          <t>knickgelenk öffnet nicht im automatikbetrieb</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>klemmt in op150</t>
+          <t>kolbenstange fährt nicht in ausgangsposition. rob tech informiert</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>klemmt in op150</t>
+          <t>kolbenstange fährt nicht in ausgangsposition. rob tech informiert</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>knickgelenk</t>
+          <t>kolbenstange passt nicht in die bohrung</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>knickgelenk</t>
+          <t>kolbenstange passt nicht in die bohrung</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>knickgelenk kabel angeschmort rob tech informiert</t>
+          <t>kollision mit geöffnetem schwenkspanner, rechte seite</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>knickgelenk kabel angeschmort rob tech informiert</t>
+          <t>kollision mit geöffnetem schwenkspanner, rechte seite</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2356,87 +2356,87 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>knickgelenk öffnet nicht im automatikbetrieb.</t>
+          <t>kollission in op 150</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>knickgelenk öffnet nicht im automatikbetrieb.</t>
+          <t>kollission in op 150</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>knickgelenk öffnet nicht.</t>
+          <t>kollision in op 150</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>knickgelenk öffnet nicht.</t>
+          <t>kollission in op 150</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kolbenstange fährt nicht in ausgangsposition. rob tech informiert</t>
+          <t>l : 2814</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>kolbenstange fährt nicht in ausgangsposition. rob tech informiert</t>
+          <t>l : 2814</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kolbenstange passt nicht in die bohrung</t>
+          <t>l: 2814</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>kolbenstange passt nicht in die bohrung</t>
+          <t>l: 2814</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kollision in op 150.</t>
+          <t>l:2814</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>kollision in op 150.</t>
+          <t>l:2814</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kollision mit geöffnetem schwenkspanner, rechte seite.</t>
+          <t>l=2714</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>kollision mit geöffnetem schwenkspanner, rechte seite.</t>
+          <t>l=2714</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2446,42 +2446,42 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kollission in op 150</t>
+          <t>l=2764</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>kollission in op 150</t>
+          <t>l=2764</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>l : 2814</t>
+          <t>l=2814</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>l : 2814</t>
+          <t>l=2814</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>l : 2814 / einzelaufträge</t>
+          <t>l=2814 deckblech manuell ablegen</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>l : 2814 / einzelaufträge</t>
+          <t>l=2814 deckblech manuell ablegen</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2491,147 +2491,147 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>l : 2814 db gestell 2.5</t>
+          <t>l=2814 r02 hat das deckblech falsch abgelegt</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>l : 2814 db gestell 2.5</t>
+          <t>l=2814 r02 hat das deckblech falsch abgelegt</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>l : 2814.</t>
+          <t>legt bauteil nicht in op 25 b li ab. räumen</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>l : 2814.</t>
+          <t>legt bauteil nicht in op 25 b li ab. räumen</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>l: 2739.</t>
+          <t>leoni</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>l: 2739.</t>
+          <t>leoni</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>l: 2750</t>
+          <t>leonifehler</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>l: 2750</t>
+          <t>leonifehler</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>l: 2814</t>
+          <t>lässt bauteil in op 150 nicht los</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>l: 2814</t>
+          <t>lässt bauteil in op 150 nicht los</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>l: 2814.</t>
+          <t>magnetgreifer gereinigt</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>l: 2814.</t>
+          <t>magnetgreifer gereinigt</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>123</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>l: 2900.</t>
+          <t>manuell in op 100 l eingelegt</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>l: 2900.</t>
+          <t>manuell in op 100 l eingelegt</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>l:2814</t>
+          <t>mes puffer bekommt keine aufträge mehr. problem unbekannt</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>l:2814</t>
+          <t>mes puffer bekommt keine aufträge mehr. problem unbekannt</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>l=2714</t>
+          <t>messfehler, netzwerkverbindungsfehler</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>l=2714</t>
+          <t>messfehler, netzwerkverbindungsfehler</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>l=2764</t>
+          <t>motorschutzschalter ausgelöst</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>l=2764</t>
+          <t>motorschutzschalter ausgelöst</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2641,27 +2641,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>l=2814</t>
+          <t>neu referenzieren</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>l=2814</t>
+          <t>neu referenzieren</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>l=2814 deckblech manuell ablegen.</t>
+          <t>neu referenziert</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>l=2814 deckblech manuell ablegen.</t>
+          <t>neu referenziert</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2671,27 +2671,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>l=2814 r02 hat das deckblech falsch abgelegt.</t>
+          <t>nimmt kein rollprofil aus 1.1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>l=2814 r02 hat das deckblech falsch abgelegt.</t>
+          <t>nimmt kein rollprofil aus 1.1</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>legt bauteil nicht in op 25 b li ab. räumen</t>
+          <t>not aus, netzteil defekt</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>legt bauteil nicht in op 25 b li ab. räumen</t>
+          <t>not aus, netzteil defekt</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2701,12 +2701,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>leoni</t>
+          <t>notaus in automatikbetrieb ausgelöst</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>leoni</t>
+          <t>notaus in automatikbetrieb ausgelöst</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2716,57 +2716,57 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>leoni störung ,brenner kontrolieren</t>
+          <t>nur 2 schweisser</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>leoni störung ,brenner kontrolieren</t>
+          <t>nur 2 schweisser</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>leonifehler.</t>
+          <t>nur 2 schweißer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>leonifehler.</t>
+          <t>nur 2 schweißer</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>lin.-einheit fährt nicht auf position, l: 2514.</t>
+          <t>ohne fehlermeldung</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>lin.-einheit fährt nicht auf position, l: 2514.</t>
+          <t>ohne fehlermeldung</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>lässt bauteil in op 150 nicht los</t>
+          <t>ohne fehlermeldung stehen geblieben</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>lässt bauteil in op 150 nicht los</t>
+          <t>ohne fehlermeldung stehen geblieben</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2776,42 +2776,42 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>magnetgreifer gereinigt</t>
+          <t>ohne meldung</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>magnetgreifer gereinigt</t>
+          <t>ohne meldung</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>manuell in op 100 l eingelegt.</t>
+          <t>ohne störung</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>manuell in op 100 l eingelegt.</t>
+          <t>ohne störung</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>mes puffer bekommt keine aufträge mehr. problem unbekannt</t>
+          <t>op 180 aktiv</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>mes puffer bekommt keine aufträge mehr. problem unbekannt</t>
+          <t>op 180 aktiv</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2821,12 +2821,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>messfehler, netzwerkverbindungsfehler.</t>
+          <t>op 180 aktiviert!</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>messfehler, netzwerkverbindungsfehler.</t>
+          <t>op 180 aktiviert!</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2836,27 +2836,27 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>neu referenzieren.</t>
+          <t>op 90l und op 40l räumen</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>neu referenzieren.</t>
+          <t>op 90l und op 40l räumen</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>neu referenziert.</t>
+          <t>per hand sägen lassen</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>neu referenziert.</t>
+          <t>per hand sägen lassen</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2866,177 +2866,177 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>nimmt kein rollprofil aus 1.1</t>
+          <t>programmfehler, greifer defekt, räumen</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>nimmt kein rollprofil aus 1.1</t>
+          <t>programmfehler, greifer defekt, räumen</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>not aus, netzteil defekt</t>
+          <t>r 01 hat bauteil falsch abgelegt</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>not aus, netzteil defekt</t>
+          <t>r 01 hat bauteil falsch abgelegt</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>notaus in automatikbetrieb ausgelöst</t>
+          <t>r 01 legt bauteil falsch ab und lässt bauteile fallen, robtech informiert, anlage in stop and go, l: 2900</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>notaus in automatikbetrieb ausgelöst</t>
+          <t>r 01 legt bauteil falsch ab und lässt bauteile fallen, robtech informiert, anlage in stop and go, l: 2900</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>nur 2 schweisser</t>
+          <t>r01 hat bauteil beim einlegen in op 100 fallen gelassen, robtech informiert, l: 2900</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>nur 2 schweisser</t>
+          <t>r01 hat bauteil beim einlegen in op 100 fallen gelassen, robtech informiert, l: 2900</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>nur 2 schweißer</t>
+          <t>r01 hat bauteil falsch abgelegt</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>nur 2 schweißer</t>
+          <t>r01 hat bauteil falsch abgelegt</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>nur 2 schweißer.</t>
+          <t>r02 legt hr nicht paarig ins gestell teamleiter informiert</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>nur 2 schweißer.</t>
+          <t>r02 legt hr nicht paarig ins gestell teamleiter informiert</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ohne fehlermeldung stehen geblieben</t>
+          <t>referenzieren</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ohne fehlermeldung stehen geblieben</t>
+          <t>referenzieren</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ohne fehlermeldung.</t>
+          <t>reinigung, wöchentlicher wartungsplan</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ohne fehlermeldung.</t>
+          <t>reinigung, wöchentlicher wartungsplan</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ohne fehlermeldung</t>
+          <t>rob tech informiert</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ohne fehlermeldung.</t>
+          <t>rob tech informiert</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ohne meldung</t>
+          <t>robtech informiert</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ohne meldung</t>
+          <t>rob tech informiert</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ohne störung.</t>
+          <t>rob tech informiert wegen r08 / banane getauscht</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ohne störung.</t>
+          <t>rob tech informiert wegen r08 / banane getauscht</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>op 180 aktiv</t>
+          <t>rob tech teacht die kehlnaht vom u-profil</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>op 180 aktiv</t>
+          <t>rob tech teacht die kehlnaht vom u-profil</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3046,42 +3046,42 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>op 180 aktiviert!</t>
+          <t>robtech demontiert zwecks abluftanlagentransport zum hinteren teil der heckrungenanlage, produktionsrelevante anlagen und roboterteile</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>op 180 aktiviert!</t>
+          <t>robtech demontiert zwecks abluftanlagentransport zum hinteren teil der heckrungenanlage, produktionsrelevante anlagen und roboterteile</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>op 180 deaktiviert</t>
+          <t>robtech in der anlage</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>op 180 deaktiviert</t>
+          <t>robtech in der anlage</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>op 90l und op 40l räumen</t>
+          <t>robtech u. bmb in der anlage</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>op 90l und op 40l räumen</t>
+          <t>robtech u. bmb in der anlage</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3091,12 +3091,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>passiv gestellt</t>
+          <t>rollprofil an auflage festgeschweißt</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>passiv gestellt</t>
+          <t>rollprofil an auflage festgeschweißt</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3106,12 +3106,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>per hand sägen lassen</t>
+          <t>rungen nacharbeiten</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>per hand sägen lassen</t>
+          <t>rungen nacharbeiten</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3121,12 +3121,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>programmfehler, greifer defekt, räumen</t>
+          <t>räumen</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>programmfehler, greifer defekt, räumen</t>
+          <t>räumen</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3136,27 +3136,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>r 01 hat bauteil falsch abgelegt</t>
+          <t>schaltzustandfehler</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>r 01 hat bauteil falsch abgelegt</t>
+          <t>schaltzustandfehler</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>r 01 legt bauteil falsch ab und lässt bauteile fallen, robtech informiert, anlage in stop and go, l: 2900.</t>
+          <t>scharnierlager in t1 geschweißt</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>r 01 legt bauteil falsch ab und lässt bauteile fallen, robtech informiert, anlage in stop and go, l: 2900.</t>
+          <t>scharnierlager in t1 geschweißt</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3166,12 +3166,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>r01 hat bauteil beim einlegen in op 100 fallen gelassen, robtech informiert, l: 2900.</t>
+          <t>schlacke abklopfen</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>r01 hat bauteil beim einlegen in op 100 fallen gelassen, robtech informiert, l: 2900.</t>
+          <t>schlacke abklopfen</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3181,102 +3181,102 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>r01 hat bauteil falsch abgelegt</t>
+          <t>schlechte schweißqualität, robtech in der anlage</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>r01 hat bauteil falsch abgelegt</t>
+          <t>schlechte schweißqualität, robtech in der anlage</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>r02 legt hr nicht paarig ins gestell teamleiter informiert</t>
+          <t>schlosser in der anlage</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>r02 legt hr nicht paarig ins gestell teamleiter informiert</t>
+          <t>schlosser in der anlage</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>referenzieren</t>
+          <t>schubladenzuweisung</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>referenzieren</t>
+          <t>schubladenzuweisung</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>referenzieren.</t>
+          <t>schweißdraht bewegt sich bei achsenbewegung zurück, zündfehler,suchfehler, robtech in der anlage, anlage in stop and go</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>referenzieren.</t>
+          <t>schweißdraht bewegt sich bei achsenbewegung zurück, zündfehler,suchfehler, robtech in der anlage, anlage in stop and go</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>reinigung, wöchentlicher wartungsplan</t>
+          <t>schweißdraht bewegt sich bei achsenbewegung zurück, zündfehler,suchfehler, robtech in der anlage, anlage in stop and go, 2 schweißer arbeiten rungen nach</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>reinigung, wöchentlicher wartungsplan</t>
+          <t>schweißdraht bewegt sich bei achsenbewegung zurück, zündfehler,suchfehler, robtech in der anlage, anlage in stop and go, 2 schweißer arbeiten rungen nach</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>rob tech informiert</t>
+          <t>schweißqualität n.i.o, robtech in der anlage</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>rob tech informiert</t>
+          <t>schweißqualität n.i.o, robtech in der anlage</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>robtech informiert</t>
+          <t>schweißt nicht rob tech informiert drahtseele getauscht</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>rob tech informiert</t>
+          <t>schweißt nicht rob tech informiert drahtseele getauscht</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3286,12 +3286,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>rob tech informiert wegen r08 / banane getauscht</t>
+          <t>schwenkspanner mitte spannt nicht deckblech nicht gut</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>rob tech informiert wegen r08 / banane getauscht</t>
+          <t>schwenkspanner mitte spannt nicht deckblech nicht gut</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3301,12 +3301,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>rob tech teacht die kehlnaht vom u-profil</t>
+          <t>schwenkspanner mitte undicht beim schließen. schlosser informiert.14:15</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>rob tech teacht die kehlnaht vom u-profil</t>
+          <t>schwenkspanner mitte undicht beim schließen. schlosser informiert.14:15</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3316,12 +3316,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>rob tech teacht suchfahrt nach</t>
+          <t>schwenkspanner mittig</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>rob tech teacht suchfahrt nach</t>
+          <t>schwenkspanner mittig</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3331,57 +3331,57 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>rob tech teacht suchfahrt nach wöchentliche reinigung</t>
+          <t>sensor defekt</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>rob tech teacht suchfahrt nach wöchentliche reinigung</t>
+          <t>sensor defekt</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>robtech demontiert zwecks abluftanlagentransport zum hinteren teil der heckrungenanlage, produktionsrelevante anlagen und roboterteile.</t>
+          <t>sensor defekt rob tech informiert</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>robtech demontiert zwecks abluftanlagentransport zum hinteren teil der heckrungenanlage, produktionsrelevante anlagen und roboterteile.</t>
+          <t>sensor defekt rob tech informiert</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>robtech in der anlage.</t>
+          <t>sensor defekt, rob tech informiert</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>robtech in der anlage.</t>
+          <t>sensor defekt rob tech informiert</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>robtech informiert.</t>
+          <t>sensor defekt , rob tech informiert</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>robtech informiert.</t>
+          <t>sensor defekt rob tech informiert</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3391,27 +3391,27 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>robtech u. bmb in der anlage.</t>
+          <t>sensor gereinigt</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>robtech u. bmb in der anlage.</t>
+          <t>sensor gereinigt</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>robtech und schlosser informiert</t>
+          <t>sensor schaltet durchgehend. sensor getauscht</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>robtech und schlosser informiert</t>
+          <t>sensor schaltet durchgehend. sensor getauscht</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3421,102 +3421,102 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>rollprofil an auflage festgeschweißt</t>
+          <t>sensor schaltet nicht</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>rollprofil an auflage festgeschweißt</t>
+          <t>sensor schaltet nicht</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>rungen nacharbeiten.</t>
+          <t>sicherheitskarte + u4-53k2</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>rungen nacharbeiten.</t>
+          <t>sicherheitskarte + u4-53k2</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>räumen</t>
+          <t>spanner gibt kein signal das geloest ist</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>räumen</t>
+          <t>spanner gibt kein signal das geloest ist</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>schaltzustandfehler.</t>
+          <t>spanner schließt nicht richtig</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>schaltzustandfehler.</t>
+          <t>spanner schließt nicht richtig</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>scharnierlager in t1 geschweißt.</t>
+          <t>spanner öffnet nicht</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>scharnierlager in t1 geschweißt.</t>
+          <t>spanner öffnet nicht</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>schlacke abklopfen</t>
+          <t>steckt in brennerreinigung fest</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>schlacke abklopfen</t>
+          <t>steckt in brennerreinigung fest</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>schlechte schweißqualität, robtech in der anlage.</t>
+          <t>steckt in brennerreinigung fest rob tech informiert</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>schlechte schweißqualität, robtech in der anlage.</t>
+          <t>steckt in brennerreinigung fest rob tech informiert</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3526,357 +3526,357 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>schlosser in der anlage.</t>
+          <t>steckt in der brennerreinigung fest</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>schlosser in der anlage.</t>
+          <t>steckt in der brennerreinigung fest</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>schubladenzuweisung</t>
+          <t>streik</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>schubladenzuweisung</t>
+          <t>streik</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>schweißdraht bewegt sich bei achsenbewegung zurück, zündfehler,suchfehler, robtech in der anlage, anlage in stop and go, 2 schweißer arbeiten rungen nach.</t>
+          <t>strom und gasdüse sauber gemacht</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>schweißdraht bewegt sich bei achsenbewegung zurück, zündfehler,suchfehler, robtech in der anlage, anlage in stop and go, 2 schweißer arbeiten rungen nach.</t>
+          <t>strom und gasdüse sauber gemacht</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>schweißqualität n.i.o, robtech in der anlage.</t>
+          <t>suchfahrt</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>schweißqualität n.i.o, robtech in der anlage.</t>
+          <t>suchfahrt</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>schweißt nicht rob tech informiert drahtseele getauscht</t>
+          <t>suchfahrtfehler</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>schweißt nicht rob tech informiert drahtseele getauscht</t>
+          <t>suchfahrtfehler</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>schwenkspanner mitte spannt nicht deckblech nicht gut</t>
+          <t>suchfehler</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>schwenkspanner mitte spannt nicht deckblech nicht gut</t>
+          <t>suchfehler</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>schwenkspanner mitte undicht beim schließen. schlosser informiert.14:15</t>
+          <t>sägeblatt getauscht</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>schwenkspanner mitte undicht beim schließen. schlosser informiert.14:15</t>
+          <t>sägeblatt getauscht</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>schwenkspanner mittig</t>
+          <t>sägeblatt tauschen</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>schwenkspanner mittig</t>
+          <t>sägeblatt tauschen</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>sensor defekt</t>
+          <t>verbindungsfehler zwischen brenner und schweißgerät, robtech informiert</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>sensor defekt</t>
+          <t>verbindungsfehler zwischen brenner und schweißgerät, robtech informiert</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>sensor defekt rob tech informiert</t>
+          <t>verriegelung von schublade 3 klemmt, wird in der störung als schublade 2 geführt</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>sensor defekt rob tech informiert</t>
+          <t>verriegelung von schublade 3 klemmt, wird in der störung als schublade 2 geführt</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>sensor defekt, rob tech informiert</t>
+          <t>versammlung</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>sensor defekt rob tech informiert</t>
+          <t>versammlung</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>sensor defekt , rob tech informiert</t>
+          <t>warten auf befüllung 1.3</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>sensor defekt rob tech informiert</t>
+          <t>warten auf befüllung 1.3</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>sensor gereinigt.</t>
+          <t>warten auf c$flag in op 100 l. ohne meldung</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>sensor gereinigt.</t>
+          <t>warten auf c$flag in op 100 l. ohne meldung</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>sensor schaltet durchgehend. sensor getauscht</t>
+          <t>warten auf db</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>sensor schaltet durchgehend. sensor getauscht</t>
+          <t>warten auf db</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>sensor schaltet nicht</t>
+          <t>warten auf db anlage kpl leer</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>sensor schaltet nicht</t>
+          <t>warten auf db anlage kpl leer</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>sicherheitskarte + u4-53k2</t>
+          <t>wartung/reinigung!!! rob tech in der anlage</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>sicherheitskarte + u4-53k2</t>
+          <t>wartung/reinigung!!! rob tech in der anlage</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>spanner schließt nicht richtig</t>
+          <t>wochenreinigung</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>spanner schließt nicht richtig</t>
+          <t>wochenreinigung</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>spanner öffnet nicht.</t>
+          <t>wochenreinigung, robtech u. fronius servicemitarbeiter in der anlage</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>spanner öffnet nicht.</t>
+          <t>wochenreinigung, robtech u. fronius servicemitarbeiter in der anlage</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>steckt in brennerreinigung fest</t>
+          <t>wöchentliche reinigung</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>steckt in brennerreinigung fest</t>
+          <t>wöchentliche reinigung</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>steckt in brennerreinigung fest.</t>
+          <t>wöchentliche/monatliche wartung, reinigung</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>steckt in brennerreinigung fest</t>
+          <t>wöchentliche/monatliche wartung, reinigung</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>steckt in brennerreinigung fest rob tech informiert</t>
+          <t>wöchentlicher wartungsplan</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>steckt in brennerreinigung fest rob tech informiert</t>
+          <t>wöchentlicher wartungsplan</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>steckt in der brennerreinigung fest.</t>
+          <t>zylinder austauschen, robtech u. schlosser in der anlage</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>steckt in der brennerreinigung fest.</t>
+          <t>zylinder austauschen, robtech u. schlosser in der anlage</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>steckt in der brennerreinigung fest</t>
+          <t>zylinder gereinigt</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>steckt in der brennerreinigung fest.</t>
+          <t>zylinder gereinigt</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>strom und gasdüse sauber gemacht</t>
+          <t>zylinder öffnet nicht</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>strom und gasdüse sauber gemacht</t>
+          <t>zylinder öffnet nicht</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3886,375 +3886,15 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>suchfahrt</t>
+          <t>zündfehler</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>suchfahrt</t>
+          <t>zündfehler</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>suchfahrtfehler</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>suchfahrtfehler</t>
-        </is>
-      </c>
-      <c r="C233" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>suchfahrtfehler, ohne störung.</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>suchfahrtfehler, ohne störung.</t>
-        </is>
-      </c>
-      <c r="C234" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>suchfahrtfehler.</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>suchfahrtfehler.</t>
-        </is>
-      </c>
-      <c r="C235" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>suchfehler.</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>suchfehler.</t>
-        </is>
-      </c>
-      <c r="C236" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>sägeblatt getauscht.</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>sägeblatt getauscht.</t>
-        </is>
-      </c>
-      <c r="C237" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>sägeblatt getauscht</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>sägeblatt getauscht.</t>
-        </is>
-      </c>
-      <c r="C238" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>sägeblatt tauschen.</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>sägeblatt tauschen.</t>
-        </is>
-      </c>
-      <c r="C239" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>verbindungsfehler zwischen brenner und schweißgerät, robtech informiert.</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>verbindungsfehler zwischen brenner und schweißgerät, robtech informiert.</t>
-        </is>
-      </c>
-      <c r="C240" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>verriegelung von schublade 3 klemmt, wird in der störung als schublade 2 geführt.</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>verriegelung von schublade 3 klemmt, wird in der störung als schublade 2 geführt.</t>
-        </is>
-      </c>
-      <c r="C241" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>warten auf befüllung 1.3</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>warten auf befüllung 1.3</t>
-        </is>
-      </c>
-      <c r="C242" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>warten auf c$flag</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>warten auf c$flag</t>
-        </is>
-      </c>
-      <c r="C243" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>warten auf c$flag in op 100 l. ohne meldung</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>warten auf c$flag in op 100 l. ohne meldung</t>
-        </is>
-      </c>
-      <c r="C244" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>warten auf db</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>warten auf db</t>
-        </is>
-      </c>
-      <c r="C245" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>warten auf db anlage kpl leer</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>warten auf db anlage kpl leer</t>
-        </is>
-      </c>
-      <c r="C246" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>wartung/reinigung!!! rob tech in der anlage</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>wartung/reinigung!!! rob tech in der anlage</t>
-        </is>
-      </c>
-      <c r="C247" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>wochenreinigung, robtech u. fronius servicemitarbeiter in der anlage.</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>wochenreinigung, robtech u. fronius servicemitarbeiter in der anlage.</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>wochenreinigung.</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>wochenreinigung.</t>
-        </is>
-      </c>
-      <c r="C249" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>wöchentliche reinigung</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>wöchentliche reinigung</t>
-        </is>
-      </c>
-      <c r="C250" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>wöchentliche/monatliche wartung, reinigung.</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>wöchentliche/monatliche wartung, reinigung.</t>
-        </is>
-      </c>
-      <c r="C251" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>wöchentlicher wartungsplan</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>wöchentlicher wartungsplan</t>
-        </is>
-      </c>
-      <c r="C252" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>zylinder austauschen, robtech u. schlosser in der anlage.</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>zylinder austauschen, robtech u. schlosser in der anlage.</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>zylinder gereinigt</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>zylinder gereinigt</t>
-        </is>
-      </c>
-      <c r="C254" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>zylinder öffnet nicht</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>zylinder öffnet nicht</t>
-        </is>
-      </c>
-      <c r="C255" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>zündfehler</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>zündfehler</t>
-        </is>
-      </c>
-      <c r="C256" t="n">
         <v>4</v>
       </c>
     </row>
